--- a/quotation/resources/견적서_template.xlsx
+++ b/quotation/resources/견적서_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkddl\Desktop\dev\.cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD47F14B-D1F2-4C4A-A88C-0F1A745A41D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39CEFECB-5789-4A69-B942-9CD535771BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3210" yWindow="4185" windowWidth="25590" windowHeight="11295" tabRatio="797" xr2:uid="{FDB72DB4-4D47-4F07-9205-F16317D584F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="797" xr2:uid="{44528EB1-9146-4792-BF25-D87325030B57}"/>
   </bookViews>
   <sheets>
     <sheet name="TOTAL" sheetId="8" r:id="rId1"/>
@@ -215,80 +215,6 @@
   </si>
   <si>
     <r>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="HY헤드라인M"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>단위</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="HY헤드라인M"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>천원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="HY헤드라인M"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부가세</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="HY헤드라인M"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>별도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t>종</t>
     </r>
     <r>
@@ -377,95 +303,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>견적</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>유효기간</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> : </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>견적</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>후</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="돋움"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>주</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>수신 :  귀중</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -479,6 +316,14 @@
   </si>
   <si>
     <t>NO : Trialinfo-24-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(단위: 천원, 부가세 별도)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>견적 유효기간 : 견적 후 2주</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -641,13 +486,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FFFFFF99"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -1049,9 +894,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1079,14 +921,17 @@
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1150,7 +995,7 @@
         <xdr:cNvPr id="7186" name="Text Box 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC5DCC45-F548-F06B-E184-F8DC0BBC1556}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ED915F1-20E1-4C7C-4997-B1C6072B25FC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1705,10 +1550,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7265" name="Picture 19" descr="trialinfo">
+        <xdr:cNvPr id="7275" name="Picture 19" descr="trialinfo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{916BB4B9-34F1-F972-E062-6108B52C044D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D401833-8478-4E25-CA90-C7AD637D381C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1779,10 +1624,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="7266" name="Group 20">
+        <xdr:cNvPr id="7276" name="Group 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F0345A6-39C3-53B0-7F3E-4F16A5309FE3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52769FE6-014D-16EE-0173-AA6529387208}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1800,10 +1645,10 @@
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="7267" name="Rectangle 21">
+          <xdr:cNvPr id="7277" name="Rectangle 21">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97A4FA21-8EDF-8A66-5EB6-E1CAFFF7D600}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{590A1F12-2069-C92C-36E4-7C65FB099953}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1849,7 +1694,7 @@
           <xdr:cNvPr id="7190" name="Text Box 22">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE2D2708-D1CA-AAD6-3CA6-3DC48EA0BB1E}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06D0156B-232E-347F-43B2-CF332CE35EF5}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1965,10 +1810,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12395" name="Picture 33" descr="trialinfo">
+        <xdr:cNvPr id="12397" name="Picture 33" descr="trialinfo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB76D2AE-5603-B1D8-19A7-29B976FE79B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3AD0D54-3F85-1A78-EC22-902F467FD1DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2376,7 +2221,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8AED31-E560-4476-85E1-67D9F8AA80C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3FA8180-67BE-4AFC-B673-4FC66BFE064A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2404,8 +2249,8 @@
       <c r="H1" s="52"/>
     </row>
     <row r="2" spans="2:9" s="8" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="79" t="s">
-        <v>26</v>
+      <c r="B2" s="78" t="s">
+        <v>24</v>
       </c>
       <c r="C2" s="40"/>
       <c r="D2" s="70"/>
@@ -2415,10 +2260,10 @@
       <c r="H2" s="55"/>
     </row>
     <row r="3" spans="2:9" s="8" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="80" t="s">
-        <v>20</v>
+      <c r="B3" s="79" t="s">
+        <v>19</v>
       </c>
-      <c r="C3" s="86"/>
+      <c r="C3" s="85"/>
       <c r="D3" s="71"/>
       <c r="E3" s="13"/>
       <c r="F3" s="56"/>
@@ -2426,8 +2271,8 @@
       <c r="H3" s="55"/>
     </row>
     <row r="4" spans="2:9" s="8" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="81" t="s">
-        <v>23</v>
+      <c r="B4" s="80" t="s">
+        <v>21</v>
       </c>
       <c r="C4" s="39"/>
       <c r="D4" s="71"/>
@@ -2436,56 +2281,56 @@
       <c r="G4" s="57"/>
       <c r="H4" s="58"/>
     </row>
-    <row r="5" spans="2:9" s="8" customFormat="1" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="88" t="s">
-        <v>22</v>
+    <row r="5" spans="2:9" s="8" customFormat="1" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="90" t="s">
+        <v>26</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="72"/>
       <c r="F5" s="59"/>
       <c r="G5" s="60"/>
-      <c r="H5" s="78" t="s">
+      <c r="H5" s="89" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" s="18" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" s="18" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="93" t="s">
+      <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="61" t="s">
+      <c r="G6" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="61" t="s">
-        <v>19</v>
-      </c>
       <c r="H6" s="95" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:9" s="18" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B7" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="85" t="s">
+      <c r="C7" s="84" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="94"/>
-      <c r="E7" s="82" t="s">
+      <c r="E7" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="83" t="s">
+      <c r="F7" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="84" t="s">
+      <c r="G7" s="83" t="s">
         <v>4</v>
       </c>
       <c r="H7" s="96"/>
@@ -3200,7 +3045,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787EB87C-EE7B-4314-B0F3-0686B5C86945}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB13FB47-CA87-4E46-BA6E-952A0E690831}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3220,7 +3065,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="87"/>
+      <c r="B1" s="86"/>
       <c r="C1" s="91"/>
       <c r="D1" s="97"/>
       <c r="E1" s="97"/>
@@ -3238,7 +3083,7 @@
     </row>
     <row r="3" spans="2:9" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="37"/>
-      <c r="C3" s="86"/>
+      <c r="C3" s="85"/>
       <c r="D3" s="12"/>
       <c r="E3" s="42"/>
       <c r="F3" s="14"/>
@@ -3256,7 +3101,7 @@
     </row>
     <row r="5" spans="2:9" s="8" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="10"/>
@@ -3286,8 +3131,8 @@
       <c r="G6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="89" t="s">
-        <v>25</v>
+      <c r="H6" s="87" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:9" s="18" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -3307,7 +3152,7 @@
       <c r="G7" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="90" t="s">
+      <c r="H7" s="88" t="s">
         <v>5</v>
       </c>
     </row>

--- a/quotation/resources/견적서_template.xlsx
+++ b/quotation/resources/견적서_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkddl\Desktop\dev\.cache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39CEFECB-5789-4A69-B942-9CD535771BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CB82E0F-8A8A-4A6A-AEBD-AFCA20A7E46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="797" xr2:uid="{44528EB1-9146-4792-BF25-D87325030B57}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="797" xr2:uid="{A6D3A3AF-1E53-4B72-B862-08EE26EEBFEE}"/>
   </bookViews>
   <sheets>
     <sheet name="TOTAL" sheetId="8" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>ITEM</t>
   </si>
@@ -137,80 +137,6 @@
   </si>
   <si>
     <t>ITEM</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="HY헤드라인M"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>단위</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="HY헤드라인M"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>천원</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="HY헤드라인M"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부가세</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="HY헤드라인M"/>
-        <family val="1"/>
-        <charset val="129"/>
-      </rPr>
-      <t>별도</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -769,9 +695,6 @@
     <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -932,6 +855,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -995,7 +921,7 @@
         <xdr:cNvPr id="7186" name="Text Box 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ED915F1-20E1-4C7C-4997-B1C6072B25FC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A326AC1B-720A-2AC2-1689-DF0CC00F91B5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1550,10 +1476,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7275" name="Picture 19" descr="trialinfo">
+        <xdr:cNvPr id="7280" name="Picture 19" descr="trialinfo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D401833-8478-4E25-CA90-C7AD637D381C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDF4E07D-CF8C-75C0-9959-B065A7D16AB7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1624,10 +1550,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="7276" name="Group 20">
+        <xdr:cNvPr id="7281" name="Group 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52769FE6-014D-16EE-0173-AA6529387208}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CC6B3C5-6C91-8446-85A7-F1D9F06E02A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1645,10 +1571,10 @@
       </xdr:grpSpPr>
       <xdr:sp macro="" textlink="">
         <xdr:nvSpPr>
-          <xdr:cNvPr id="7277" name="Rectangle 21">
+          <xdr:cNvPr id="7282" name="Rectangle 21">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{590A1F12-2069-C92C-36E4-7C65FB099953}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE996C8D-BBF7-B6BC-F796-AEC951984C88}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1694,7 +1620,7 @@
           <xdr:cNvPr id="7190" name="Text Box 22">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06D0156B-232E-347F-43B2-CF332CE35EF5}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBBECC7E-773E-37E4-D8FC-42ED1C472CB0}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -1810,10 +1736,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12397" name="Picture 33" descr="trialinfo">
+        <xdr:cNvPr id="12398" name="Picture 33" descr="trialinfo">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F3AD0D54-3F85-1A78-EC22-902F467FD1DB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F38C7E7E-F053-47D0-93A4-E46891D67B87}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2221,7 +2147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3FA8180-67BE-4AFC-B673-4FC66BFE064A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3847F08D-BE41-4C70-A681-7136A1D59127}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2229,13 +2155,13 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.109375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="10.5546875" style="47" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" style="51" customWidth="1"/>
-    <col min="4" max="4" width="31.6640625" style="75" customWidth="1"/>
+    <col min="2" max="2" width="10.5546875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="50" customWidth="1"/>
+    <col min="4" max="4" width="31.6640625" style="74" customWidth="1"/>
     <col min="5" max="5" width="4.6640625" style="7" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" style="68" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" style="68" customWidth="1"/>
-    <col min="8" max="8" width="11.21875" style="69" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" style="67" customWidth="1"/>
+    <col min="7" max="7" width="10.21875" style="67" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" style="68" customWidth="1"/>
     <col min="9" max="9" width="2.21875" style="7" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="7"/>
   </cols>
@@ -2246,784 +2172,784 @@
       <c r="E1" s="92"/>
       <c r="F1" s="92"/>
       <c r="G1" s="92"/>
-      <c r="H1" s="52"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="2:9" s="8" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="77" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="39"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="54"/>
+    </row>
+    <row r="3" spans="2:9" s="8" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="84"/>
+      <c r="D3" s="70"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="54"/>
+    </row>
+    <row r="4" spans="2:9" s="8" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="38"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="57"/>
+    </row>
+    <row r="5" spans="2:9" s="8" customFormat="1" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="71"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="88" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="55"/>
-    </row>
-    <row r="3" spans="2:9" s="8" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="79" t="s">
-        <v>19</v>
+    </row>
+    <row r="6" spans="2:9" s="18" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="3" t="s">
+        <v>12</v>
       </c>
-      <c r="C3" s="85"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="55"/>
-    </row>
-    <row r="4" spans="2:9" s="8" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="80" t="s">
+      <c r="C6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="57"/>
-      <c r="G4" s="57"/>
-      <c r="H4" s="58"/>
-    </row>
-    <row r="5" spans="2:9" s="8" customFormat="1" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="90" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="72"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="89" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9" s="18" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="93" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="61" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" s="61" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" s="95" t="s">
-        <v>22</v>
-      </c>
     </row>
     <row r="7" spans="2:9" s="18" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="84" t="s">
+      <c r="C7" s="83" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="94"/>
-      <c r="E7" s="81" t="s">
+      <c r="E7" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="82" t="s">
+      <c r="F7" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="83" t="s">
+      <c r="G7" s="82" t="s">
         <v>4</v>
       </c>
       <c r="H7" s="96"/>
     </row>
     <row r="8" spans="2:9" s="24" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="45"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="73"/>
-      <c r="F8" s="62"/>
-      <c r="G8" s="62"/>
-      <c r="H8" s="63"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="72"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="62"/>
       <c r="I8" s="25"/>
     </row>
     <row r="9" spans="2:9" s="24" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B9" s="45"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="73"/>
-      <c r="F9" s="62"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="63"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="72"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="62"/>
     </row>
     <row r="10" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B10" s="46"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="74"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="66"/>
-      <c r="H10" s="67"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="73"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="66"/>
     </row>
     <row r="11" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B11" s="46"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="74"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="66"/>
-      <c r="H11" s="67"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="73"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
+      <c r="H11" s="66"/>
     </row>
     <row r="12" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B12" s="46"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="74"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="67"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="73"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="66"/>
     </row>
     <row r="13" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B13" s="46"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="74"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="67"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="73"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="66"/>
     </row>
     <row r="14" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B14" s="46"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="74"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="67"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="73"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="66"/>
     </row>
     <row r="15" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B15" s="46"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="74"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="67"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="73"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="64"/>
+      <c r="H15" s="66"/>
     </row>
     <row r="16" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B16" s="46"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="74"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="67"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="73"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="64"/>
+      <c r="H16" s="66"/>
     </row>
     <row r="17" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B17" s="46"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="74"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="67"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="73"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="66"/>
     </row>
     <row r="18" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B18" s="46"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="74"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="67"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="73"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="64"/>
+      <c r="H18" s="66"/>
     </row>
     <row r="19" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B19" s="46"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="74"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="67"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="73"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="66"/>
     </row>
     <row r="20" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B20" s="46"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="74"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="67"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="73"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="64"/>
+      <c r="H20" s="66"/>
     </row>
     <row r="21" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B21" s="46"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="74"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="67"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="73"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="66"/>
     </row>
     <row r="22" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B22" s="46"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="74"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="67"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="73"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="64"/>
+      <c r="H22" s="66"/>
     </row>
     <row r="23" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B23" s="46"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="74"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="67"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="49"/>
+      <c r="D23" s="73"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="66"/>
     </row>
     <row r="24" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B24" s="46"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="74"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="67"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="73"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="64"/>
+      <c r="H24" s="66"/>
     </row>
     <row r="25" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B25" s="46"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="74"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="67"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="49"/>
+      <c r="D25" s="73"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="64"/>
+      <c r="H25" s="66"/>
     </row>
     <row r="26" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B26" s="46"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="74"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="67"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="73"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="64"/>
+      <c r="H26" s="66"/>
     </row>
     <row r="27" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B27" s="46"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="74"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="67"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="73"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="64"/>
+      <c r="H27" s="66"/>
     </row>
     <row r="28" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B28" s="46"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="74"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="67"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="73"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="64"/>
+      <c r="H28" s="66"/>
     </row>
     <row r="29" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B29" s="46"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="74"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="67"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="73"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="66"/>
     </row>
     <row r="30" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B30" s="46"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="74"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="67"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="73"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="64"/>
+      <c r="H30" s="66"/>
     </row>
     <row r="31" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B31" s="46"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="74"/>
-      <c r="F31" s="65"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="67"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="73"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="64"/>
+      <c r="H31" s="66"/>
     </row>
     <row r="32" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B32" s="46"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="74"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="67"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="73"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="66"/>
     </row>
     <row r="33" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B33" s="46"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="74"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="65"/>
-      <c r="H33" s="67"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="73"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="66"/>
     </row>
     <row r="34" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B34" s="46"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="74"/>
-      <c r="F34" s="65"/>
-      <c r="G34" s="65"/>
-      <c r="H34" s="67"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="49"/>
+      <c r="D34" s="73"/>
+      <c r="F34" s="64"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="66"/>
     </row>
     <row r="35" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B35" s="46"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="74"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="67"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="73"/>
+      <c r="F35" s="64"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="66"/>
     </row>
     <row r="36" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B36" s="46"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="74"/>
-      <c r="F36" s="65"/>
-      <c r="G36" s="65"/>
-      <c r="H36" s="67"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="49"/>
+      <c r="D36" s="73"/>
+      <c r="F36" s="64"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="66"/>
     </row>
     <row r="37" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B37" s="46"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="74"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="67"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="73"/>
+      <c r="F37" s="64"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="66"/>
     </row>
     <row r="38" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B38" s="46"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="74"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="67"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="49"/>
+      <c r="D38" s="73"/>
+      <c r="F38" s="64"/>
+      <c r="G38" s="64"/>
+      <c r="H38" s="66"/>
     </row>
     <row r="39" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B39" s="46"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="74"/>
-      <c r="F39" s="65"/>
-      <c r="G39" s="65"/>
-      <c r="H39" s="67"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="49"/>
+      <c r="D39" s="73"/>
+      <c r="F39" s="64"/>
+      <c r="G39" s="64"/>
+      <c r="H39" s="66"/>
     </row>
     <row r="40" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B40" s="46"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="74"/>
-      <c r="F40" s="65"/>
-      <c r="G40" s="65"/>
-      <c r="H40" s="67"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="73"/>
+      <c r="F40" s="64"/>
+      <c r="G40" s="64"/>
+      <c r="H40" s="66"/>
     </row>
     <row r="41" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B41" s="46"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="74"/>
-      <c r="F41" s="65"/>
-      <c r="G41" s="65"/>
-      <c r="H41" s="67"/>
+      <c r="B41" s="45"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="73"/>
+      <c r="F41" s="64"/>
+      <c r="G41" s="64"/>
+      <c r="H41" s="66"/>
     </row>
     <row r="42" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B42" s="46"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="74"/>
-      <c r="F42" s="65"/>
-      <c r="G42" s="65"/>
-      <c r="H42" s="67"/>
+      <c r="B42" s="45"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="73"/>
+      <c r="F42" s="64"/>
+      <c r="G42" s="64"/>
+      <c r="H42" s="66"/>
     </row>
     <row r="43" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B43" s="46"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="74"/>
-      <c r="F43" s="65"/>
-      <c r="G43" s="65"/>
-      <c r="H43" s="67"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="73"/>
+      <c r="F43" s="64"/>
+      <c r="G43" s="64"/>
+      <c r="H43" s="66"/>
     </row>
     <row r="44" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B44" s="46"/>
-      <c r="C44" s="50"/>
-      <c r="D44" s="74"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="65"/>
-      <c r="H44" s="67"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="49"/>
+      <c r="D44" s="73"/>
+      <c r="F44" s="64"/>
+      <c r="G44" s="64"/>
+      <c r="H44" s="66"/>
     </row>
     <row r="45" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B45" s="46"/>
-      <c r="C45" s="50"/>
-      <c r="D45" s="74"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="65"/>
-      <c r="H45" s="67"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="73"/>
+      <c r="F45" s="64"/>
+      <c r="G45" s="64"/>
+      <c r="H45" s="66"/>
     </row>
     <row r="46" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B46" s="46"/>
-      <c r="C46" s="50"/>
-      <c r="D46" s="74"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="67"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="73"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="66"/>
     </row>
     <row r="47" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B47" s="46"/>
-      <c r="C47" s="50"/>
-      <c r="D47" s="74"/>
-      <c r="F47" s="65"/>
-      <c r="G47" s="65"/>
-      <c r="H47" s="67"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="73"/>
+      <c r="F47" s="64"/>
+      <c r="G47" s="64"/>
+      <c r="H47" s="66"/>
     </row>
     <row r="48" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B48" s="46"/>
-      <c r="C48" s="50"/>
-      <c r="D48" s="74"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="65"/>
-      <c r="H48" s="67"/>
+      <c r="B48" s="45"/>
+      <c r="C48" s="49"/>
+      <c r="D48" s="73"/>
+      <c r="F48" s="64"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="66"/>
     </row>
     <row r="49" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B49" s="46"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="74"/>
-      <c r="F49" s="65"/>
-      <c r="G49" s="65"/>
-      <c r="H49" s="67"/>
+      <c r="B49" s="45"/>
+      <c r="C49" s="49"/>
+      <c r="D49" s="73"/>
+      <c r="F49" s="64"/>
+      <c r="G49" s="64"/>
+      <c r="H49" s="66"/>
     </row>
     <row r="50" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B50" s="46"/>
-      <c r="C50" s="50"/>
-      <c r="D50" s="74"/>
-      <c r="F50" s="65"/>
-      <c r="G50" s="65"/>
-      <c r="H50" s="67"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="49"/>
+      <c r="D50" s="73"/>
+      <c r="F50" s="64"/>
+      <c r="G50" s="64"/>
+      <c r="H50" s="66"/>
     </row>
     <row r="51" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B51" s="46"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="74"/>
-      <c r="F51" s="65"/>
-      <c r="G51" s="65"/>
-      <c r="H51" s="67"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="49"/>
+      <c r="D51" s="73"/>
+      <c r="F51" s="64"/>
+      <c r="G51" s="64"/>
+      <c r="H51" s="66"/>
     </row>
     <row r="52" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B52" s="46"/>
-      <c r="C52" s="50"/>
-      <c r="D52" s="74"/>
-      <c r="F52" s="65"/>
-      <c r="G52" s="65"/>
-      <c r="H52" s="67"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="73"/>
+      <c r="F52" s="64"/>
+      <c r="G52" s="64"/>
+      <c r="H52" s="66"/>
     </row>
     <row r="53" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B53" s="46"/>
-      <c r="C53" s="50"/>
-      <c r="D53" s="74"/>
-      <c r="F53" s="65"/>
-      <c r="G53" s="65"/>
-      <c r="H53" s="67"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="49"/>
+      <c r="D53" s="73"/>
+      <c r="F53" s="64"/>
+      <c r="G53" s="64"/>
+      <c r="H53" s="66"/>
     </row>
     <row r="54" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B54" s="46"/>
-      <c r="C54" s="50"/>
-      <c r="D54" s="74"/>
-      <c r="F54" s="65"/>
-      <c r="G54" s="65"/>
-      <c r="H54" s="67"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="49"/>
+      <c r="D54" s="73"/>
+      <c r="F54" s="64"/>
+      <c r="G54" s="64"/>
+      <c r="H54" s="66"/>
     </row>
     <row r="55" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B55" s="46"/>
-      <c r="C55" s="50"/>
-      <c r="D55" s="74"/>
-      <c r="F55" s="65"/>
-      <c r="G55" s="65"/>
-      <c r="H55" s="67"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="73"/>
+      <c r="F55" s="64"/>
+      <c r="G55" s="64"/>
+      <c r="H55" s="66"/>
     </row>
     <row r="56" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B56" s="46"/>
-      <c r="C56" s="50"/>
-      <c r="D56" s="74"/>
-      <c r="F56" s="65"/>
-      <c r="G56" s="65"/>
-      <c r="H56" s="67"/>
+      <c r="B56" s="45"/>
+      <c r="C56" s="49"/>
+      <c r="D56" s="73"/>
+      <c r="F56" s="64"/>
+      <c r="G56" s="64"/>
+      <c r="H56" s="66"/>
     </row>
     <row r="57" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B57" s="46"/>
-      <c r="C57" s="50"/>
-      <c r="D57" s="74"/>
-      <c r="F57" s="65"/>
-      <c r="G57" s="65"/>
-      <c r="H57" s="67"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="49"/>
+      <c r="D57" s="73"/>
+      <c r="F57" s="64"/>
+      <c r="G57" s="64"/>
+      <c r="H57" s="66"/>
     </row>
     <row r="58" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B58" s="46"/>
-      <c r="C58" s="50"/>
-      <c r="D58" s="74"/>
-      <c r="F58" s="65"/>
-      <c r="G58" s="65"/>
-      <c r="H58" s="67"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="73"/>
+      <c r="F58" s="64"/>
+      <c r="G58" s="64"/>
+      <c r="H58" s="66"/>
     </row>
     <row r="59" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B59" s="46"/>
-      <c r="C59" s="50"/>
-      <c r="D59" s="74"/>
-      <c r="F59" s="65"/>
-      <c r="G59" s="65"/>
-      <c r="H59" s="67"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="49"/>
+      <c r="D59" s="73"/>
+      <c r="F59" s="64"/>
+      <c r="G59" s="64"/>
+      <c r="H59" s="66"/>
     </row>
     <row r="60" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B60" s="46"/>
-      <c r="C60" s="50"/>
-      <c r="D60" s="74"/>
-      <c r="F60" s="65"/>
-      <c r="G60" s="65"/>
-      <c r="H60" s="67"/>
+      <c r="B60" s="45"/>
+      <c r="C60" s="49"/>
+      <c r="D60" s="73"/>
+      <c r="F60" s="64"/>
+      <c r="G60" s="64"/>
+      <c r="H60" s="66"/>
     </row>
     <row r="61" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B61" s="46"/>
-      <c r="C61" s="50"/>
-      <c r="D61" s="74"/>
-      <c r="F61" s="65"/>
-      <c r="G61" s="65"/>
-      <c r="H61" s="67"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="49"/>
+      <c r="D61" s="73"/>
+      <c r="F61" s="64"/>
+      <c r="G61" s="64"/>
+      <c r="H61" s="66"/>
     </row>
     <row r="62" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B62" s="46"/>
-      <c r="C62" s="50"/>
-      <c r="D62" s="74"/>
-      <c r="F62" s="65"/>
-      <c r="G62" s="65"/>
-      <c r="H62" s="67"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="49"/>
+      <c r="D62" s="73"/>
+      <c r="F62" s="64"/>
+      <c r="G62" s="64"/>
+      <c r="H62" s="66"/>
     </row>
     <row r="63" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B63" s="46"/>
-      <c r="C63" s="50"/>
-      <c r="D63" s="74"/>
-      <c r="F63" s="65"/>
-      <c r="G63" s="65"/>
-      <c r="H63" s="67"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="49"/>
+      <c r="D63" s="73"/>
+      <c r="F63" s="64"/>
+      <c r="G63" s="64"/>
+      <c r="H63" s="66"/>
     </row>
     <row r="64" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B64" s="46"/>
-      <c r="C64" s="50"/>
-      <c r="D64" s="74"/>
-      <c r="F64" s="65"/>
-      <c r="G64" s="65"/>
-      <c r="H64" s="67"/>
+      <c r="B64" s="45"/>
+      <c r="C64" s="49"/>
+      <c r="D64" s="73"/>
+      <c r="F64" s="64"/>
+      <c r="G64" s="64"/>
+      <c r="H64" s="66"/>
     </row>
     <row r="65" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B65" s="46"/>
-      <c r="C65" s="50"/>
-      <c r="D65" s="74"/>
-      <c r="F65" s="65"/>
-      <c r="G65" s="65"/>
-      <c r="H65" s="67"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="49"/>
+      <c r="D65" s="73"/>
+      <c r="F65" s="64"/>
+      <c r="G65" s="64"/>
+      <c r="H65" s="66"/>
     </row>
     <row r="66" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B66" s="46"/>
-      <c r="C66" s="50"/>
-      <c r="D66" s="74"/>
-      <c r="F66" s="65"/>
-      <c r="G66" s="65"/>
-      <c r="H66" s="67"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="49"/>
+      <c r="D66" s="73"/>
+      <c r="F66" s="64"/>
+      <c r="G66" s="64"/>
+      <c r="H66" s="66"/>
     </row>
     <row r="67" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B67" s="46"/>
-      <c r="C67" s="50"/>
-      <c r="D67" s="74"/>
-      <c r="F67" s="65"/>
-      <c r="G67" s="65"/>
-      <c r="H67" s="67"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="49"/>
+      <c r="D67" s="73"/>
+      <c r="F67" s="64"/>
+      <c r="G67" s="64"/>
+      <c r="H67" s="66"/>
     </row>
     <row r="68" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B68" s="46"/>
-      <c r="C68" s="50"/>
-      <c r="D68" s="74"/>
-      <c r="F68" s="65"/>
-      <c r="G68" s="65"/>
-      <c r="H68" s="67"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="49"/>
+      <c r="D68" s="73"/>
+      <c r="F68" s="64"/>
+      <c r="G68" s="64"/>
+      <c r="H68" s="66"/>
     </row>
     <row r="69" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B69" s="46"/>
-      <c r="C69" s="50"/>
-      <c r="D69" s="74"/>
-      <c r="F69" s="65"/>
-      <c r="G69" s="65"/>
-      <c r="H69" s="67"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="49"/>
+      <c r="D69" s="73"/>
+      <c r="F69" s="64"/>
+      <c r="G69" s="64"/>
+      <c r="H69" s="66"/>
     </row>
     <row r="70" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B70" s="46"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="74"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="65"/>
-      <c r="H70" s="67"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="49"/>
+      <c r="D70" s="73"/>
+      <c r="F70" s="64"/>
+      <c r="G70" s="64"/>
+      <c r="H70" s="66"/>
     </row>
     <row r="71" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B71" s="46"/>
-      <c r="C71" s="50"/>
-      <c r="D71" s="74"/>
-      <c r="F71" s="65"/>
-      <c r="G71" s="65"/>
-      <c r="H71" s="67"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="49"/>
+      <c r="D71" s="73"/>
+      <c r="F71" s="64"/>
+      <c r="G71" s="64"/>
+      <c r="H71" s="66"/>
     </row>
     <row r="72" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B72" s="46"/>
-      <c r="C72" s="50"/>
-      <c r="D72" s="74"/>
-      <c r="F72" s="65"/>
-      <c r="G72" s="65"/>
-      <c r="H72" s="67"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="49"/>
+      <c r="D72" s="73"/>
+      <c r="F72" s="64"/>
+      <c r="G72" s="64"/>
+      <c r="H72" s="66"/>
     </row>
     <row r="73" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B73" s="46"/>
-      <c r="C73" s="50"/>
-      <c r="D73" s="74"/>
-      <c r="F73" s="65"/>
-      <c r="G73" s="65"/>
-      <c r="H73" s="67"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="49"/>
+      <c r="D73" s="73"/>
+      <c r="F73" s="64"/>
+      <c r="G73" s="64"/>
+      <c r="H73" s="66"/>
     </row>
     <row r="74" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B74" s="46"/>
-      <c r="C74" s="50"/>
-      <c r="D74" s="74"/>
-      <c r="F74" s="65"/>
-      <c r="G74" s="65"/>
-      <c r="H74" s="67"/>
+      <c r="B74" s="45"/>
+      <c r="C74" s="49"/>
+      <c r="D74" s="73"/>
+      <c r="F74" s="64"/>
+      <c r="G74" s="64"/>
+      <c r="H74" s="66"/>
     </row>
     <row r="75" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B75" s="46"/>
-      <c r="C75" s="50"/>
-      <c r="D75" s="74"/>
-      <c r="F75" s="65"/>
-      <c r="G75" s="65"/>
-      <c r="H75" s="67"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="49"/>
+      <c r="D75" s="73"/>
+      <c r="F75" s="64"/>
+      <c r="G75" s="64"/>
+      <c r="H75" s="66"/>
     </row>
     <row r="76" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B76" s="46"/>
-      <c r="C76" s="50"/>
-      <c r="D76" s="74"/>
-      <c r="F76" s="65"/>
-      <c r="G76" s="65"/>
-      <c r="H76" s="67"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="49"/>
+      <c r="D76" s="73"/>
+      <c r="F76" s="64"/>
+      <c r="G76" s="64"/>
+      <c r="H76" s="66"/>
     </row>
     <row r="77" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B77" s="46"/>
-      <c r="C77" s="50"/>
-      <c r="D77" s="74"/>
-      <c r="F77" s="65"/>
-      <c r="G77" s="65"/>
-      <c r="H77" s="67"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="49"/>
+      <c r="D77" s="73"/>
+      <c r="F77" s="64"/>
+      <c r="G77" s="64"/>
+      <c r="H77" s="66"/>
     </row>
     <row r="78" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B78" s="46"/>
-      <c r="C78" s="50"/>
-      <c r="D78" s="74"/>
-      <c r="F78" s="65"/>
-      <c r="G78" s="65"/>
-      <c r="H78" s="67"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="49"/>
+      <c r="D78" s="73"/>
+      <c r="F78" s="64"/>
+      <c r="G78" s="64"/>
+      <c r="H78" s="66"/>
     </row>
     <row r="79" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B79" s="46"/>
-      <c r="C79" s="50"/>
-      <c r="D79" s="74"/>
-      <c r="F79" s="65"/>
-      <c r="G79" s="65"/>
-      <c r="H79" s="67"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="49"/>
+      <c r="D79" s="73"/>
+      <c r="F79" s="64"/>
+      <c r="G79" s="64"/>
+      <c r="H79" s="66"/>
     </row>
     <row r="80" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B80" s="46"/>
-      <c r="C80" s="50"/>
-      <c r="D80" s="74"/>
-      <c r="F80" s="65"/>
-      <c r="G80" s="65"/>
-      <c r="H80" s="67"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="49"/>
+      <c r="D80" s="73"/>
+      <c r="F80" s="64"/>
+      <c r="G80" s="64"/>
+      <c r="H80" s="66"/>
     </row>
     <row r="81" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B81" s="46"/>
-      <c r="C81" s="50"/>
-      <c r="D81" s="74"/>
-      <c r="F81" s="65"/>
-      <c r="G81" s="65"/>
-      <c r="H81" s="67"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="49"/>
+      <c r="D81" s="73"/>
+      <c r="F81" s="64"/>
+      <c r="G81" s="64"/>
+      <c r="H81" s="66"/>
     </row>
     <row r="82" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B82" s="46"/>
-      <c r="C82" s="50"/>
-      <c r="D82" s="74"/>
-      <c r="F82" s="65"/>
-      <c r="G82" s="65"/>
-      <c r="H82" s="67"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="49"/>
+      <c r="D82" s="73"/>
+      <c r="F82" s="64"/>
+      <c r="G82" s="64"/>
+      <c r="H82" s="66"/>
     </row>
     <row r="83" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B83" s="46"/>
-      <c r="C83" s="50"/>
-      <c r="D83" s="74"/>
-      <c r="F83" s="65"/>
-      <c r="G83" s="65"/>
-      <c r="H83" s="67"/>
+      <c r="B83" s="45"/>
+      <c r="C83" s="49"/>
+      <c r="D83" s="73"/>
+      <c r="F83" s="64"/>
+      <c r="G83" s="64"/>
+      <c r="H83" s="66"/>
     </row>
     <row r="84" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B84" s="46"/>
-      <c r="C84" s="50"/>
-      <c r="D84" s="74"/>
-      <c r="F84" s="65"/>
-      <c r="G84" s="65"/>
-      <c r="H84" s="67"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="49"/>
+      <c r="D84" s="73"/>
+      <c r="F84" s="64"/>
+      <c r="G84" s="64"/>
+      <c r="H84" s="66"/>
     </row>
     <row r="85" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B85" s="46"/>
-      <c r="C85" s="50"/>
-      <c r="D85" s="74"/>
-      <c r="F85" s="65"/>
-      <c r="G85" s="65"/>
-      <c r="H85" s="67"/>
+      <c r="B85" s="45"/>
+      <c r="C85" s="49"/>
+      <c r="D85" s="73"/>
+      <c r="F85" s="64"/>
+      <c r="G85" s="64"/>
+      <c r="H85" s="66"/>
     </row>
     <row r="86" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B86" s="46"/>
-      <c r="C86" s="50"/>
-      <c r="D86" s="74"/>
-      <c r="F86" s="65"/>
-      <c r="G86" s="65"/>
-      <c r="H86" s="67"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="49"/>
+      <c r="D86" s="73"/>
+      <c r="F86" s="64"/>
+      <c r="G86" s="64"/>
+      <c r="H86" s="66"/>
     </row>
     <row r="87" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B87" s="46"/>
-      <c r="C87" s="50"/>
-      <c r="D87" s="74"/>
-      <c r="F87" s="65"/>
-      <c r="G87" s="65"/>
-      <c r="H87" s="67"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="49"/>
+      <c r="D87" s="73"/>
+      <c r="F87" s="64"/>
+      <c r="G87" s="64"/>
+      <c r="H87" s="66"/>
     </row>
     <row r="88" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B88" s="46"/>
-      <c r="C88" s="50"/>
-      <c r="D88" s="74"/>
-      <c r="F88" s="65"/>
-      <c r="G88" s="65"/>
-      <c r="H88" s="67"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="49"/>
+      <c r="D88" s="73"/>
+      <c r="F88" s="64"/>
+      <c r="G88" s="64"/>
+      <c r="H88" s="66"/>
     </row>
     <row r="89" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B89" s="46"/>
-      <c r="C89" s="50"/>
-      <c r="D89" s="74"/>
-      <c r="F89" s="65"/>
-      <c r="G89" s="65"/>
-      <c r="H89" s="67"/>
+      <c r="B89" s="45"/>
+      <c r="C89" s="49"/>
+      <c r="D89" s="73"/>
+      <c r="F89" s="64"/>
+      <c r="G89" s="64"/>
+      <c r="H89" s="66"/>
     </row>
     <row r="90" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B90" s="46"/>
-      <c r="C90" s="50"/>
-      <c r="D90" s="74"/>
-      <c r="F90" s="65"/>
-      <c r="G90" s="65"/>
-      <c r="H90" s="67"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="49"/>
+      <c r="D90" s="73"/>
+      <c r="F90" s="64"/>
+      <c r="G90" s="64"/>
+      <c r="H90" s="66"/>
     </row>
     <row r="91" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B91" s="46"/>
-      <c r="C91" s="50"/>
-      <c r="D91" s="74"/>
-      <c r="F91" s="65"/>
-      <c r="G91" s="65"/>
-      <c r="H91" s="67"/>
+      <c r="B91" s="45"/>
+      <c r="C91" s="49"/>
+      <c r="D91" s="73"/>
+      <c r="F91" s="64"/>
+      <c r="G91" s="64"/>
+      <c r="H91" s="66"/>
     </row>
     <row r="92" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="B92" s="46"/>
-      <c r="C92" s="50"/>
-      <c r="D92" s="74"/>
-      <c r="F92" s="65"/>
-      <c r="G92" s="65"/>
-      <c r="H92" s="67"/>
+      <c r="B92" s="45"/>
+      <c r="C92" s="49"/>
+      <c r="D92" s="73"/>
+      <c r="F92" s="64"/>
+      <c r="G92" s="64"/>
+      <c r="H92" s="66"/>
     </row>
     <row r="93" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="B93" s="47"/>
-      <c r="C93" s="51"/>
-      <c r="D93" s="75"/>
+      <c r="B93" s="46"/>
+      <c r="C93" s="50"/>
+      <c r="D93" s="74"/>
       <c r="E93" s="7"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
-      <c r="H93" s="69"/>
+      <c r="F93" s="67"/>
+      <c r="G93" s="67"/>
+      <c r="H93" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3045,7 +2971,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB13FB47-CA87-4E46-BA6E-952A0E690831}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA1011F4-86EC-442A-A395-F6F9B7445046}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3054,9 +2980,9 @@
   <cols>
     <col min="1" max="1" width="2.21875" style="7" customWidth="1"/>
     <col min="2" max="2" width="10.44140625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="51" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="50" customWidth="1"/>
     <col min="4" max="4" width="33.109375" style="7" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="47" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="46" customWidth="1"/>
     <col min="6" max="6" width="9.44140625" style="30" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" style="30" customWidth="1"/>
     <col min="8" max="8" width="9.33203125" style="7" customWidth="1"/>
@@ -3065,7 +2991,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="86"/>
+      <c r="B1" s="85"/>
       <c r="C1" s="91"/>
       <c r="D1" s="97"/>
       <c r="E1" s="97"/>
@@ -3074,42 +3000,42 @@
       <c r="H1" s="32"/>
     </row>
     <row r="2" spans="2:9" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="37"/>
-      <c r="C2" s="40"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="39"/>
       <c r="D2" s="31"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="36"/>
-      <c r="H2" s="35"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="35"/>
+      <c r="H2" s="34"/>
     </row>
     <row r="3" spans="2:9" s="8" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="37"/>
-      <c r="C3" s="85"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="84"/>
       <c r="D3" s="12"/>
-      <c r="E3" s="42"/>
+      <c r="E3" s="41"/>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
-      <c r="H3" s="35"/>
+      <c r="H3" s="34"/>
     </row>
     <row r="4" spans="2:9" s="8" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="2"/>
-      <c r="C4" s="39"/>
+      <c r="C4" s="38"/>
       <c r="D4" s="12"/>
-      <c r="E4" s="43"/>
+      <c r="E4" s="42"/>
       <c r="F4" s="16"/>
       <c r="G4" s="16"/>
       <c r="H4" s="13"/>
     </row>
     <row r="5" spans="2:9" s="8" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="10"/>
-      <c r="E5" s="44"/>
+      <c r="E5" s="43"/>
       <c r="F5" s="15"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="33" t="s">
-        <v>12</v>
+      <c r="G5" s="37"/>
+      <c r="H5" s="90" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="2:9" s="18" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -3131,8 +3057,8 @@
       <c r="G6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="87" t="s">
-        <v>23</v>
+      <c r="H6" s="86" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="2:9" s="18" customFormat="1" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -3152,527 +3078,527 @@
       <c r="G7" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="88" t="s">
+      <c r="H7" s="87" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:9" s="24" customFormat="1" ht="10.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="C8" s="48"/>
-      <c r="E8" s="45"/>
+      <c r="C8" s="47"/>
+      <c r="E8" s="44"/>
       <c r="F8" s="26"/>
       <c r="G8" s="26"/>
       <c r="I8" s="25"/>
     </row>
     <row r="9" spans="2:9" s="24" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C9" s="49"/>
-      <c r="E9" s="45"/>
+      <c r="C9" s="48"/>
+      <c r="E9" s="44"/>
       <c r="F9" s="26"/>
       <c r="G9" s="27"/>
     </row>
     <row r="10" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C10" s="50"/>
-      <c r="E10" s="46"/>
+      <c r="C10" s="49"/>
+      <c r="E10" s="45"/>
       <c r="F10" s="28"/>
       <c r="G10" s="29"/>
     </row>
     <row r="11" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C11" s="50"/>
-      <c r="E11" s="46"/>
+      <c r="C11" s="49"/>
+      <c r="E11" s="45"/>
       <c r="F11" s="28"/>
       <c r="G11" s="29"/>
     </row>
     <row r="12" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C12" s="50"/>
-      <c r="E12" s="46"/>
+      <c r="C12" s="49"/>
+      <c r="E12" s="45"/>
       <c r="F12" s="28"/>
       <c r="G12" s="28"/>
     </row>
     <row r="13" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C13" s="50"/>
-      <c r="E13" s="46"/>
+      <c r="C13" s="49"/>
+      <c r="E13" s="45"/>
       <c r="F13" s="28"/>
       <c r="G13" s="28"/>
     </row>
     <row r="14" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C14" s="50"/>
-      <c r="E14" s="46"/>
+      <c r="C14" s="49"/>
+      <c r="E14" s="45"/>
       <c r="F14" s="28"/>
       <c r="G14" s="28"/>
     </row>
     <row r="15" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C15" s="50"/>
-      <c r="E15" s="46"/>
+      <c r="C15" s="49"/>
+      <c r="E15" s="45"/>
       <c r="F15" s="28"/>
       <c r="G15" s="28"/>
     </row>
     <row r="16" spans="2:9" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C16" s="50"/>
-      <c r="E16" s="46"/>
+      <c r="C16" s="49"/>
+      <c r="E16" s="45"/>
       <c r="F16" s="28"/>
       <c r="G16" s="28"/>
     </row>
     <row r="17" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C17" s="50"/>
-      <c r="E17" s="46"/>
+      <c r="C17" s="49"/>
+      <c r="E17" s="45"/>
       <c r="F17" s="28"/>
       <c r="G17" s="28"/>
     </row>
     <row r="18" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C18" s="50"/>
-      <c r="E18" s="46"/>
+      <c r="C18" s="49"/>
+      <c r="E18" s="45"/>
       <c r="F18" s="28"/>
       <c r="G18" s="28"/>
     </row>
     <row r="19" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C19" s="50"/>
-      <c r="E19" s="46"/>
+      <c r="C19" s="49"/>
+      <c r="E19" s="45"/>
       <c r="F19" s="28"/>
       <c r="G19" s="28"/>
     </row>
     <row r="20" spans="3:7" s="18" customFormat="1" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="C20" s="50"/>
+      <c r="C20" s="49"/>
       <c r="D20"/>
-      <c r="E20" s="46"/>
+      <c r="E20" s="45"/>
       <c r="F20" s="28"/>
       <c r="G20" s="28"/>
     </row>
     <row r="21" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C21" s="50"/>
-      <c r="E21" s="46"/>
+      <c r="C21" s="49"/>
+      <c r="E21" s="45"/>
       <c r="F21" s="28"/>
       <c r="G21" s="28"/>
     </row>
     <row r="22" spans="3:7" s="18" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C22" s="76"/>
-      <c r="E22" s="46"/>
+      <c r="C22" s="75"/>
+      <c r="E22" s="45"/>
       <c r="F22" s="28"/>
       <c r="G22" s="28"/>
     </row>
     <row r="23" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C23" s="50"/>
-      <c r="E23" s="46"/>
+      <c r="C23" s="49"/>
+      <c r="E23" s="45"/>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
     </row>
     <row r="24" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C24" s="50"/>
-      <c r="E24" s="46"/>
+      <c r="C24" s="49"/>
+      <c r="E24" s="45"/>
       <c r="F24" s="28"/>
       <c r="G24" s="28"/>
     </row>
     <row r="25" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C25" s="50"/>
-      <c r="E25" s="46"/>
+      <c r="C25" s="49"/>
+      <c r="E25" s="45"/>
       <c r="F25" s="28"/>
       <c r="G25" s="28"/>
     </row>
     <row r="26" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C26" s="50"/>
-      <c r="E26" s="46"/>
+      <c r="C26" s="49"/>
+      <c r="E26" s="45"/>
       <c r="F26" s="28"/>
       <c r="G26" s="28"/>
     </row>
     <row r="27" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C27" s="50"/>
-      <c r="E27" s="46"/>
+      <c r="C27" s="49"/>
+      <c r="E27" s="45"/>
       <c r="F27" s="28"/>
       <c r="G27" s="28"/>
     </row>
     <row r="28" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C28" s="50"/>
-      <c r="E28" s="46"/>
+      <c r="C28" s="49"/>
+      <c r="E28" s="45"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28"/>
     </row>
     <row r="29" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C29" s="50"/>
-      <c r="E29" s="46"/>
+      <c r="C29" s="49"/>
+      <c r="E29" s="45"/>
       <c r="F29" s="28"/>
       <c r="G29" s="28"/>
     </row>
     <row r="30" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C30" s="50"/>
-      <c r="E30" s="46"/>
+      <c r="C30" s="49"/>
+      <c r="E30" s="45"/>
       <c r="F30" s="28"/>
       <c r="G30" s="28"/>
     </row>
     <row r="31" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C31" s="50"/>
-      <c r="E31" s="46"/>
+      <c r="C31" s="49"/>
+      <c r="E31" s="45"/>
       <c r="F31" s="28"/>
       <c r="G31" s="28"/>
     </row>
     <row r="32" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C32" s="50"/>
-      <c r="E32" s="46"/>
+      <c r="C32" s="49"/>
+      <c r="E32" s="45"/>
       <c r="F32" s="28"/>
       <c r="G32" s="28"/>
     </row>
     <row r="33" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C33" s="50"/>
-      <c r="E33" s="46"/>
+      <c r="C33" s="49"/>
+      <c r="E33" s="45"/>
       <c r="F33" s="28"/>
       <c r="G33" s="28"/>
     </row>
     <row r="34" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C34" s="50"/>
-      <c r="E34" s="46"/>
+      <c r="C34" s="49"/>
+      <c r="E34" s="45"/>
       <c r="F34" s="28"/>
       <c r="G34" s="28"/>
     </row>
     <row r="35" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C35" s="50"/>
-      <c r="E35" s="46"/>
+      <c r="C35" s="49"/>
+      <c r="E35" s="45"/>
       <c r="F35" s="28"/>
       <c r="G35" s="28"/>
     </row>
     <row r="36" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C36" s="50"/>
-      <c r="E36" s="46"/>
+      <c r="C36" s="49"/>
+      <c r="E36" s="45"/>
       <c r="F36" s="28"/>
       <c r="G36" s="28"/>
     </row>
     <row r="37" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C37" s="50"/>
-      <c r="E37" s="46"/>
+      <c r="C37" s="49"/>
+      <c r="E37" s="45"/>
       <c r="F37" s="28"/>
       <c r="G37" s="28"/>
     </row>
     <row r="38" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C38" s="50"/>
-      <c r="E38" s="46"/>
+      <c r="C38" s="49"/>
+      <c r="E38" s="45"/>
       <c r="F38" s="28"/>
       <c r="G38" s="28"/>
     </row>
     <row r="39" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C39" s="50"/>
-      <c r="E39" s="46"/>
+      <c r="C39" s="49"/>
+      <c r="E39" s="45"/>
       <c r="F39" s="28"/>
       <c r="G39" s="28"/>
     </row>
     <row r="40" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C40" s="50"/>
-      <c r="E40" s="46"/>
+      <c r="C40" s="49"/>
+      <c r="E40" s="45"/>
       <c r="F40" s="28"/>
       <c r="G40" s="28"/>
     </row>
     <row r="41" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C41" s="50"/>
-      <c r="E41" s="46"/>
+      <c r="C41" s="49"/>
+      <c r="E41" s="45"/>
       <c r="F41" s="28"/>
       <c r="G41" s="28"/>
     </row>
     <row r="42" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C42" s="50"/>
-      <c r="E42" s="46"/>
+      <c r="C42" s="49"/>
+      <c r="E42" s="45"/>
       <c r="F42" s="28"/>
       <c r="G42" s="28"/>
     </row>
     <row r="43" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C43" s="50"/>
-      <c r="E43" s="46"/>
+      <c r="C43" s="49"/>
+      <c r="E43" s="45"/>
       <c r="F43" s="28"/>
       <c r="G43" s="28"/>
     </row>
     <row r="44" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C44" s="50"/>
-      <c r="E44" s="46"/>
+      <c r="C44" s="49"/>
+      <c r="E44" s="45"/>
       <c r="F44" s="28"/>
       <c r="G44" s="28"/>
     </row>
     <row r="45" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C45" s="50"/>
-      <c r="E45" s="46"/>
+      <c r="C45" s="49"/>
+      <c r="E45" s="45"/>
       <c r="F45" s="28"/>
       <c r="G45" s="28"/>
     </row>
     <row r="46" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C46" s="50"/>
-      <c r="E46" s="46"/>
+      <c r="C46" s="49"/>
+      <c r="E46" s="45"/>
       <c r="F46" s="28"/>
       <c r="G46" s="28"/>
     </row>
     <row r="47" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C47" s="50"/>
-      <c r="E47" s="46"/>
+      <c r="C47" s="49"/>
+      <c r="E47" s="45"/>
       <c r="F47" s="28"/>
       <c r="G47" s="28"/>
     </row>
     <row r="48" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C48" s="50"/>
-      <c r="E48" s="46"/>
+      <c r="C48" s="49"/>
+      <c r="E48" s="45"/>
       <c r="F48" s="28"/>
       <c r="G48" s="28"/>
     </row>
     <row r="49" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C49" s="50"/>
-      <c r="E49" s="46"/>
+      <c r="C49" s="49"/>
+      <c r="E49" s="45"/>
       <c r="F49" s="28"/>
       <c r="G49" s="28"/>
     </row>
     <row r="50" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C50" s="50"/>
-      <c r="E50" s="46"/>
+      <c r="C50" s="49"/>
+      <c r="E50" s="45"/>
       <c r="F50" s="28"/>
       <c r="G50" s="28"/>
     </row>
     <row r="51" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C51" s="50"/>
-      <c r="E51" s="46"/>
+      <c r="C51" s="49"/>
+      <c r="E51" s="45"/>
       <c r="F51" s="28"/>
       <c r="G51" s="28"/>
     </row>
     <row r="52" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C52" s="50"/>
-      <c r="E52" s="46"/>
+      <c r="C52" s="49"/>
+      <c r="E52" s="45"/>
       <c r="F52" s="28"/>
       <c r="G52" s="28"/>
     </row>
     <row r="53" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C53" s="50"/>
-      <c r="E53" s="46"/>
+      <c r="C53" s="49"/>
+      <c r="E53" s="45"/>
       <c r="F53" s="28"/>
       <c r="G53" s="28"/>
     </row>
     <row r="54" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C54" s="50"/>
-      <c r="E54" s="46"/>
+      <c r="C54" s="49"/>
+      <c r="E54" s="45"/>
       <c r="F54" s="28"/>
       <c r="G54" s="28"/>
     </row>
     <row r="55" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C55" s="50"/>
-      <c r="E55" s="46"/>
+      <c r="C55" s="49"/>
+      <c r="E55" s="45"/>
       <c r="F55" s="28"/>
       <c r="G55" s="28"/>
     </row>
     <row r="56" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C56" s="50"/>
-      <c r="E56" s="46"/>
+      <c r="C56" s="49"/>
+      <c r="E56" s="45"/>
       <c r="F56" s="28"/>
       <c r="G56" s="28"/>
     </row>
     <row r="57" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C57" s="50"/>
-      <c r="E57" s="46"/>
+      <c r="C57" s="49"/>
+      <c r="E57" s="45"/>
       <c r="F57" s="28"/>
       <c r="G57" s="28"/>
     </row>
     <row r="58" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C58" s="50"/>
-      <c r="E58" s="46"/>
+      <c r="C58" s="49"/>
+      <c r="E58" s="45"/>
       <c r="F58" s="28"/>
       <c r="G58" s="28"/>
     </row>
     <row r="59" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C59" s="50"/>
-      <c r="E59" s="46"/>
+      <c r="C59" s="49"/>
+      <c r="E59" s="45"/>
       <c r="F59" s="28"/>
       <c r="G59" s="28"/>
     </row>
     <row r="60" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C60" s="50"/>
-      <c r="E60" s="46"/>
+      <c r="C60" s="49"/>
+      <c r="E60" s="45"/>
       <c r="F60" s="28"/>
       <c r="G60" s="28"/>
     </row>
     <row r="61" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C61" s="50"/>
-      <c r="E61" s="46"/>
+      <c r="C61" s="49"/>
+      <c r="E61" s="45"/>
       <c r="F61" s="28"/>
       <c r="G61" s="28"/>
     </row>
     <row r="62" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C62" s="50"/>
-      <c r="E62" s="46"/>
+      <c r="C62" s="49"/>
+      <c r="E62" s="45"/>
       <c r="F62" s="28"/>
       <c r="G62" s="28"/>
     </row>
     <row r="63" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C63" s="50"/>
-      <c r="E63" s="46"/>
+      <c r="C63" s="49"/>
+      <c r="E63" s="45"/>
       <c r="F63" s="28"/>
       <c r="G63" s="28"/>
     </row>
     <row r="64" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C64" s="50"/>
-      <c r="E64" s="46"/>
+      <c r="C64" s="49"/>
+      <c r="E64" s="45"/>
       <c r="F64" s="28"/>
       <c r="G64" s="28"/>
     </row>
     <row r="65" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C65" s="50"/>
-      <c r="E65" s="46"/>
+      <c r="C65" s="49"/>
+      <c r="E65" s="45"/>
       <c r="F65" s="28"/>
       <c r="G65" s="28"/>
     </row>
     <row r="66" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C66" s="50"/>
-      <c r="E66" s="46"/>
+      <c r="C66" s="49"/>
+      <c r="E66" s="45"/>
       <c r="F66" s="28"/>
       <c r="G66" s="28"/>
     </row>
     <row r="67" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C67" s="50"/>
-      <c r="E67" s="46"/>
+      <c r="C67" s="49"/>
+      <c r="E67" s="45"/>
       <c r="F67" s="28"/>
       <c r="G67" s="28"/>
     </row>
     <row r="68" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C68" s="50"/>
-      <c r="E68" s="46"/>
+      <c r="C68" s="49"/>
+      <c r="E68" s="45"/>
       <c r="F68" s="28"/>
       <c r="G68" s="28"/>
     </row>
     <row r="69" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C69" s="50"/>
-      <c r="E69" s="46"/>
+      <c r="C69" s="49"/>
+      <c r="E69" s="45"/>
       <c r="F69" s="28"/>
       <c r="G69" s="28"/>
     </row>
     <row r="70" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C70" s="50"/>
-      <c r="E70" s="46"/>
+      <c r="C70" s="49"/>
+      <c r="E70" s="45"/>
       <c r="F70" s="28"/>
       <c r="G70" s="28"/>
     </row>
     <row r="71" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C71" s="50"/>
-      <c r="E71" s="46"/>
+      <c r="C71" s="49"/>
+      <c r="E71" s="45"/>
       <c r="F71" s="28"/>
       <c r="G71" s="28"/>
     </row>
     <row r="72" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C72" s="50"/>
-      <c r="E72" s="46"/>
+      <c r="C72" s="49"/>
+      <c r="E72" s="45"/>
       <c r="F72" s="28"/>
       <c r="G72" s="28"/>
     </row>
     <row r="73" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C73" s="50"/>
-      <c r="E73" s="46"/>
+      <c r="C73" s="49"/>
+      <c r="E73" s="45"/>
       <c r="F73" s="28"/>
       <c r="G73" s="28"/>
     </row>
     <row r="74" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C74" s="50"/>
-      <c r="E74" s="46"/>
+      <c r="C74" s="49"/>
+      <c r="E74" s="45"/>
       <c r="F74" s="28"/>
       <c r="G74" s="28"/>
     </row>
     <row r="75" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C75" s="50"/>
-      <c r="E75" s="46"/>
+      <c r="C75" s="49"/>
+      <c r="E75" s="45"/>
       <c r="F75" s="28"/>
       <c r="G75" s="28"/>
     </row>
     <row r="76" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C76" s="50"/>
-      <c r="E76" s="46"/>
+      <c r="C76" s="49"/>
+      <c r="E76" s="45"/>
       <c r="F76" s="28"/>
       <c r="G76" s="28"/>
     </row>
     <row r="77" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C77" s="50"/>
-      <c r="E77" s="46"/>
+      <c r="C77" s="49"/>
+      <c r="E77" s="45"/>
       <c r="F77" s="28"/>
       <c r="G77" s="28"/>
     </row>
     <row r="78" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C78" s="50"/>
-      <c r="E78" s="46"/>
+      <c r="C78" s="49"/>
+      <c r="E78" s="45"/>
       <c r="F78" s="28"/>
       <c r="G78" s="28"/>
     </row>
     <row r="79" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C79" s="50"/>
-      <c r="E79" s="46"/>
+      <c r="C79" s="49"/>
+      <c r="E79" s="45"/>
       <c r="F79" s="28"/>
       <c r="G79" s="28"/>
     </row>
     <row r="80" spans="3:7" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C80" s="50"/>
-      <c r="E80" s="46"/>
+      <c r="C80" s="49"/>
+      <c r="E80" s="45"/>
       <c r="F80" s="28"/>
       <c r="G80" s="28"/>
     </row>
     <row r="81" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C81" s="50"/>
-      <c r="E81" s="46"/>
+      <c r="C81" s="49"/>
+      <c r="E81" s="45"/>
       <c r="F81" s="28"/>
       <c r="G81" s="28"/>
     </row>
     <row r="82" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C82" s="50"/>
-      <c r="E82" s="46"/>
+      <c r="C82" s="49"/>
+      <c r="E82" s="45"/>
       <c r="F82" s="28"/>
       <c r="G82" s="28"/>
     </row>
     <row r="83" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C83" s="50"/>
-      <c r="E83" s="46"/>
+      <c r="C83" s="49"/>
+      <c r="E83" s="45"/>
       <c r="F83" s="28"/>
       <c r="G83" s="28"/>
     </row>
     <row r="84" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C84" s="50"/>
-      <c r="E84" s="46"/>
+      <c r="C84" s="49"/>
+      <c r="E84" s="45"/>
       <c r="F84" s="28"/>
       <c r="G84" s="28"/>
     </row>
     <row r="85" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C85" s="50"/>
-      <c r="E85" s="46"/>
+      <c r="C85" s="49"/>
+      <c r="E85" s="45"/>
       <c r="F85" s="28"/>
       <c r="G85" s="28"/>
     </row>
     <row r="86" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C86" s="50"/>
-      <c r="E86" s="46"/>
+      <c r="C86" s="49"/>
+      <c r="E86" s="45"/>
       <c r="F86" s="28"/>
       <c r="G86" s="28"/>
     </row>
     <row r="87" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C87" s="50"/>
-      <c r="E87" s="46"/>
+      <c r="C87" s="49"/>
+      <c r="E87" s="45"/>
       <c r="F87" s="28"/>
       <c r="G87" s="28"/>
     </row>
     <row r="88" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C88" s="50"/>
-      <c r="E88" s="46"/>
+      <c r="C88" s="49"/>
+      <c r="E88" s="45"/>
       <c r="F88" s="28"/>
       <c r="G88" s="28"/>
     </row>
     <row r="89" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C89" s="50"/>
-      <c r="E89" s="46"/>
+      <c r="C89" s="49"/>
+      <c r="E89" s="45"/>
       <c r="F89" s="28"/>
       <c r="G89" s="28"/>
     </row>
     <row r="90" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C90" s="50"/>
-      <c r="E90" s="46"/>
+      <c r="C90" s="49"/>
+      <c r="E90" s="45"/>
       <c r="F90" s="28"/>
       <c r="G90" s="28"/>
     </row>
     <row r="91" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C91" s="50"/>
-      <c r="E91" s="46"/>
+      <c r="C91" s="49"/>
+      <c r="E91" s="45"/>
       <c r="F91" s="28"/>
       <c r="G91" s="28"/>
     </row>
     <row r="92" spans="2:8" s="18" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="C92" s="50"/>
-      <c r="E92" s="46"/>
+      <c r="C92" s="49"/>
+      <c r="E92" s="45"/>
       <c r="F92" s="28"/>
       <c r="G92" s="28"/>
     </row>
     <row r="93" spans="2:8" s="18" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B93" s="7"/>
-      <c r="C93" s="51"/>
+      <c r="C93" s="50"/>
       <c r="D93" s="7"/>
-      <c r="E93" s="47"/>
+      <c r="E93" s="46"/>
       <c r="F93" s="30"/>
       <c r="G93" s="30"/>
       <c r="H93" s="7"/>
